--- a/#Russia_anonymized.xlsx
+++ b/#Russia_anonymized.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10813,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10940,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10983,7 +10983,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18792,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22336,7 +22336,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22380,7 +22380,7 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22424,7 +22424,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22468,7 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22512,7 +22512,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22556,7 +22556,7 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26251,7 +26251,7 @@
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26295,7 +26295,7 @@
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26340,7 +26340,7 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
